--- a/ZonasEscolares/excels/TACNA-TACNA-CORONEL_GREGORIO_ALBARRACIN_LANCHIPA.xlsx
+++ b/ZonasEscolares/excels/TACNA-TACNA-CORONEL_GREGORIO_ALBARRACIN_LANCHIPA.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CORONEL_GREGORIO_ALBARRACIN_LANCHIPA</t>
+          <t>CORONEL GREGORIO ALBARRACIN LANCHIPA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CORONEL_GREGORIO_ALBARRACIN_LANCHIPA</t>
+          <t>CORONEL GREGORIO ALBARRACIN LANCHIPA</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CORONEL_GREGORIO_ALBARRACIN_LANCHIPA</t>
+          <t>CORONEL GREGORIO ALBARRACIN LANCHIPA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CORONEL_GREGORIO_ALBARRACIN_LANCHIPA</t>
+          <t>CORONEL GREGORIO ALBARRACIN LANCHIPA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -716,7 +716,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CORONEL_GREGORIO_ALBARRACIN_LANCHIPA</t>
+          <t>CORONEL GREGORIO ALBARRACIN LANCHIPA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -768,7 +768,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CORONEL_GREGORIO_ALBARRACIN_LANCHIPA</t>
+          <t>CORONEL GREGORIO ALBARRACIN LANCHIPA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CORONEL_GREGORIO_ALBARRACIN_LANCHIPA</t>
+          <t>CORONEL GREGORIO ALBARRACIN LANCHIPA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CORONEL_GREGORIO_ALBARRACIN_LANCHIPA</t>
+          <t>CORONEL GREGORIO ALBARRACIN LANCHIPA</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CORONEL_GREGORIO_ALBARRACIN_LANCHIPA</t>
+          <t>CORONEL GREGORIO ALBARRACIN LANCHIPA</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CORONEL_GREGORIO_ALBARRACIN_LANCHIPA</t>
+          <t>CORONEL GREGORIO ALBARRACIN LANCHIPA</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CORONEL_GREGORIO_ALBARRACIN_LANCHIPA</t>
+          <t>CORONEL GREGORIO ALBARRACIN LANCHIPA</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CORONEL_GREGORIO_ALBARRACIN_LANCHIPA</t>
+          <t>CORONEL GREGORIO ALBARRACIN LANCHIPA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CORONEL_GREGORIO_ALBARRACIN_LANCHIPA</t>
+          <t>CORONEL GREGORIO ALBARRACIN LANCHIPA</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CORONEL_GREGORIO_ALBARRACIN_LANCHIPA</t>
+          <t>CORONEL GREGORIO ALBARRACIN LANCHIPA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CORONEL_GREGORIO_ALBARRACIN_LANCHIPA</t>
+          <t>CORONEL GREGORIO ALBARRACIN LANCHIPA</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>CORONEL_GREGORIO_ALBARRACIN_LANCHIPA</t>
+          <t>CORONEL GREGORIO ALBARRACIN LANCHIPA</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CORONEL_GREGORIO_ALBARRACIN_LANCHIPA</t>
+          <t>CORONEL GREGORIO ALBARRACIN LANCHIPA</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CORONEL_GREGORIO_ALBARRACIN_LANCHIPA</t>
+          <t>CORONEL GREGORIO ALBARRACIN LANCHIPA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CORONEL_GREGORIO_ALBARRACIN_LANCHIPA</t>
+          <t>CORONEL GREGORIO ALBARRACIN LANCHIPA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CORONEL_GREGORIO_ALBARRACIN_LANCHIPA</t>
+          <t>CORONEL GREGORIO ALBARRACIN LANCHIPA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/TACNA-TACNA-CORONEL_GREGORIO_ALBARRACIN_LANCHIPA.xlsx
+++ b/ZonasEscolares/excels/TACNA-TACNA-CORONEL_GREGORIO_ALBARRACIN_LANCHIPA.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>SAN MIGUEL ARCANGEL</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-18.04626</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-70.25615000000001</v>
-      </c>
-      <c r="I2" t="n">
-        <v>41</v>
-      </c>
-      <c r="J2" t="n">
-        <v>4</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-18.04626</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-70.25615</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>419</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-18.05448</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-70.2496</v>
-      </c>
-      <c r="I3" t="n">
-        <v>151</v>
-      </c>
-      <c r="J3" t="n">
-        <v>9</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-18.05448</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-70.2496</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>42237 JORGE CHAVEZ</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-18.04038</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-70.25572</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1842</v>
-      </c>
-      <c r="J4" t="n">
-        <v>99</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-18.04038</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-70.25572</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1842</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>42238 ENRIQUE PAILLARDELLE</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-18.047217</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-70.25094199999999</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1799</v>
-      </c>
-      <c r="J5" t="n">
-        <v>93</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-18.047217</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-70.250942</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1799</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>42253 GERARDO ARIAS COPAJA</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-18.05123</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-70.25725</v>
-      </c>
-      <c r="I6" t="n">
-        <v>975</v>
-      </c>
-      <c r="J6" t="n">
-        <v>49</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-18.05123</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-70.25725</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>975</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-18.05025</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-70.24346</v>
-      </c>
-      <c r="I7" t="n">
-        <v>149</v>
-      </c>
-      <c r="J7" t="n">
-        <v>20</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-18.05025</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-70.24346</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>450 ENRIQUE DELHORME</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-18.0699</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-70.2409</v>
-      </c>
-      <c r="I8" t="n">
-        <v>213</v>
-      </c>
-      <c r="J8" t="n">
-        <v>10</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-18.0699</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-70.2409</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>456 EL CARMELO DE MARIA</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-18.08729</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-70.27736</v>
-      </c>
-      <c r="I9" t="n">
-        <v>423</v>
-      </c>
-      <c r="J9" t="n">
-        <v>21</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-18.08729</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-70.27736</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>423</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>43508 PROCER MANUEL CALDERON DE LA BARCA</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-18.0730569112003</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-70.2595473938168</v>
-      </c>
-      <c r="I10" t="n">
-        <v>775</v>
-      </c>
-      <c r="J10" t="n">
-        <v>24</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-18.0730569112003</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-70.2595473938168</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>775</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>469</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-18.05259</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-70.25391</v>
-      </c>
-      <c r="I11" t="n">
-        <v>63</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-18.05259</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-70.25391</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>42256 ESPERANZA MARTINEZ DE LOPEZ</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-18.03286</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-70.24279</v>
-      </c>
-      <c r="I12" t="n">
-        <v>665</v>
-      </c>
-      <c r="J12" t="n">
-        <v>34</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-18.03286</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-70.24279</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>42255 SANTA TERESITA DEL NIÑO JESUS</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-18.03938</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-70.24599000000001</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1004</v>
-      </c>
-      <c r="J13" t="n">
-        <v>58</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-18.03938</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-70.24599</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>426</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-18.0528</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-70.25397</v>
-      </c>
-      <c r="I14" t="n">
-        <v>65</v>
-      </c>
-      <c r="J14" t="n">
-        <v>3</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-18.0528</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-70.25397</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>LUIS ALBERTO SANCHEZ</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-18.05841</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-70.25076</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1854</v>
-      </c>
-      <c r="J15" t="n">
-        <v>99</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-18.05841</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-70.25076</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1854</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>42257 NUESTRO SEÑOR DE LA MISERICORDIA</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-18.05518</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-70.25546</v>
-      </c>
-      <c r="I16" t="n">
-        <v>345</v>
-      </c>
-      <c r="J16" t="n">
-        <v>16</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-18.05518</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-70.25546</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>345</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>DR. JOSE ANTONIO ENCINAS FRANCO</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-18.06851</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-70.24763</v>
-      </c>
-      <c r="I17" t="n">
-        <v>952</v>
-      </c>
-      <c r="J17" t="n">
-        <v>62</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-18.06851</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-70.24763</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>952</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>SANTA CRUZ</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-18.06338</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-70.25691</v>
-      </c>
-      <c r="I18" t="n">
-        <v>1031</v>
-      </c>
-      <c r="J18" t="n">
-        <v>56</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-18.06338</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-70.25691</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1031</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>SAN JOSE DE NAZARET</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-18.02703</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-70.24281000000001</v>
-      </c>
-      <c r="I19" t="n">
-        <v>501</v>
-      </c>
-      <c r="J19" t="n">
-        <v>40</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-18.02703</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-70.24281</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>501</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>EMMA GAMERO NIETO</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-18.03603</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-70.25315999999999</v>
-      </c>
-      <c r="I20" t="n">
-        <v>211</v>
-      </c>
-      <c r="J20" t="n">
-        <v>16</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-18.03603</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-70.25316</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>473 PEDRO QUINA CASTAÑON</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-18.05195</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-70.23651</v>
-      </c>
-      <c r="I21" t="n">
-        <v>241</v>
-      </c>
-      <c r="J21" t="n">
-        <v>13</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-18.05195</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-70.23651</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/TACNA-TACNA-CORONEL_GREGORIO_ALBARRACIN_LANCHIPA.xlsx
+++ b/ZonasEscolares/excels/TACNA-TACNA-CORONEL_GREGORIO_ALBARRACIN_LANCHIPA.xlsx
@@ -501,42 +501,42 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>254025</t>
+          <t>668515</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>SAN MIGUEL ARCANGEL</t>
+          <t>450 ENRIQUE DELHORME</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-18.04626</t>
+          <t>-18.0699</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-70.25615</t>
+          <t>-70.2409</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>213</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>486285</t>
+          <t>857790</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>419</t>
+          <t>473 PEDRO QUINA CASTAÑON</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-18.05448</t>
+          <t>-18.05195</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-70.2496</t>
+          <t>-70.23651</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>241</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -598,7 +598,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>486539</t>
+          <t>808686</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>42237 JORGE CHAVEZ</t>
+          <t>42257 NUESTRO SEÑOR DE LA MISERICORDIA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-18.04038</t>
+          <t>-18.05518</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-70.25572</t>
+          <t>-70.25546</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>345</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>486544</t>
+          <t>841638</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>42238 ENRIQUE PAILLARDELLE</t>
+          <t>EMMA GAMERO NIETO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-18.047217</t>
+          <t>-18.03603</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-70.250942</t>
+          <t>-70.25316</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1799</t>
+          <t>211</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>486836</t>
+          <t>623862</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>42253 GERARDO ARIAS COPAJA</t>
+          <t>SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-18.05123</t>
+          <t>-18.05025</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-70.25725</t>
+          <t>-70.24346</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>149</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,42 +811,42 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>623862</t>
+          <t>668577</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SEÑOR DE LOS MILAGROS</t>
+          <t>456 EL CARMELO DE MARIA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-18.05025</t>
+          <t>-18.08729</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-70.24346</t>
+          <t>-70.27736</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>423</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>668515</t>
+          <t>718025</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>450 ENRIQUE DELHORME</t>
+          <t>43508 PROCER MANUEL CALDERON DE LA BARCA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-18.0699</t>
+          <t>-18.0730569112003</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-70.2409</t>
+          <t>-70.2595473938168</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>775</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,37 +935,37 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>668577</t>
+          <t>728487</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>456 EL CARMELO DE MARIA</t>
+          <t>469</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-18.08729</t>
+          <t>-18.05259</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-70.27736</t>
+          <t>-70.25391</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>423</t>
+          <t>63</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -997,42 +997,42 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>718025</t>
+          <t>808460</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>43508 PROCER MANUEL CALDERON DE LA BARCA</t>
+          <t>426</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-18.0730569112003</t>
+          <t>-18.0528</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-70.2595473938168</t>
+          <t>-70.25397</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>775</t>
+          <t>65</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1059,42 +1059,42 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>728487</t>
+          <t>808441</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>469</t>
+          <t>42256 ESPERANZA MARTINEZ DE LOPEZ</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-18.05259</t>
+          <t>-18.03286</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-70.25391</t>
+          <t>-70.24279</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>665</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1121,42 +1121,42 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>808441</t>
+          <t>254025</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>42256 ESPERANZA MARTINEZ DE LOPEZ</t>
+          <t>SAN MIGUEL ARCANGEL</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-18.03286</t>
+          <t>-18.04626</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-70.24279</t>
+          <t>-70.25615</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>41</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>808455</t>
+          <t>837146</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>42255 SANTA TERESITA DEL NIÑO JESUS</t>
+          <t>SAN JOSE DE NAZARET</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-18.03938</t>
+          <t>-18.02703</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-70.24599</t>
+          <t>-70.24281</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>501</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1245,42 +1245,42 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>808460</t>
+          <t>486836</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>42253 GERARDO ARIAS COPAJA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-18.0528</t>
+          <t>-18.05123</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-70.25397</t>
+          <t>-70.25725</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>975</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>49</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>808653</t>
+          <t>809233</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>LUIS ALBERTO SANCHEZ</t>
+          <t>SANTA CRUZ</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-18.05841</t>
+          <t>-18.06338</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-70.25076</t>
+          <t>-70.25691</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1854</t>
+          <t>1031</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>56</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>808686</t>
+          <t>808455</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>42257 NUESTRO SEÑOR DE LA MISERICORDIA</t>
+          <t>42255 SANTA TERESITA DEL NIÑO JESUS</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-18.05518</t>
+          <t>-18.03938</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-70.25546</t>
+          <t>-70.24599</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>58</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>809233</t>
+          <t>486285</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SANTA CRUZ</t>
+          <t>419</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-18.06338</t>
+          <t>-18.05448</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-70.25691</t>
+          <t>-70.2496</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1031</t>
+          <t>151</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>837146</t>
+          <t>486544</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SAN JOSE DE NAZARET</t>
+          <t>42238 ENRIQUE PAILLARDELLE</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-18.02703</t>
+          <t>-18.047217</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-70.24281</t>
+          <t>-70.250942</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>501</t>
+          <t>1799</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>93</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>841638</t>
+          <t>486539</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>EMMA GAMERO NIETO</t>
+          <t>42237 JORGE CHAVEZ</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-18.03603</t>
+          <t>-18.04038</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-70.25316</t>
+          <t>-70.25572</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>99</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>857790</t>
+          <t>808653</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>473 PEDRO QUINA CASTAÑON</t>
+          <t>LUIS ALBERTO SANCHEZ</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-18.05195</t>
+          <t>-18.05841</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-70.23651</t>
+          <t>-70.25076</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>1854</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>99</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">

--- a/ZonasEscolares/excels/TACNA-TACNA-CORONEL_GREGORIO_ALBARRACIN_LANCHIPA.xlsx
+++ b/ZonasEscolares/excels/TACNA-TACNA-CORONEL_GREGORIO_ALBARRACIN_LANCHIPA.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>668515</t>
+          <t>857790</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>450 ENRIQUE DELHORME</t>
+          <t>473 PEDRO QUINA CASTAÑON</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-18.0699</t>
+          <t>241</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-70.2409</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>-18.05195</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-70.23651</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -536,7 +536,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>857790</t>
+          <t>841638</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>473 PEDRO QUINA CASTAÑON</t>
+          <t>EMMA GAMERO NIETO</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-18.05195</t>
+          <t>211</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-70.23651</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>-18.03603</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-70.25316</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -598,7 +598,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>808686</t>
+          <t>837146</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>42257 NUESTRO SEÑOR DE LA MISERICORDIA</t>
+          <t>SAN JOSE DE NAZARET</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-18.05518</t>
+          <t>501</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-70.25546</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>-18.02703</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-70.24281</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>841638</t>
+          <t>809233</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>EMMA GAMERO NIETO</t>
+          <t>SANTA CRUZ</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-18.03603</t>
+          <t>1031</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-70.25316</t>
+          <t>56</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>-18.06338</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-70.25691</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>623862</t>
+          <t>809214</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SEÑOR DE LOS MILAGROS</t>
+          <t>DR. JOSE ANTONIO ENCINAS FRANCO</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-18.05025</t>
+          <t>952</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-70.24346</t>
+          <t>62</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>-18.06851</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-70.24763</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,42 +811,42 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>668577</t>
+          <t>808686</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>456 EL CARMELO DE MARIA</t>
+          <t>42257 NUESTRO SEÑOR DE LA MISERICORDIA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-18.08729</t>
+          <t>345</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-70.27736</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>423</t>
+          <t>-18.05518</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-70.25546</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>718025</t>
+          <t>808653</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>43508 PROCER MANUEL CALDERON DE LA BARCA</t>
+          <t>LUIS ALBERTO SANCHEZ</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-18.0730569112003</t>
+          <t>1854</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-70.2595473938168</t>
+          <t>99</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>775</t>
+          <t>-18.05841</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-70.25076</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>728487</t>
+          <t>808460</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>469</t>
+          <t>426</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-18.05259</t>
+          <t>65</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-70.25391</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>-18.0528</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-70.25397</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,42 +997,42 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>808460</t>
+          <t>808455</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>42255 SANTA TERESITA DEL NIÑO JESUS</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-18.0528</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-70.25397</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>-18.03938</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-70.24599</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1069,22 +1069,22 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>-18.03286</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>-70.24279</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>665</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>34</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>254025</t>
+          <t>728487</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>SAN MIGUEL ARCANGEL</t>
+          <t>469</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-18.04626</t>
+          <t>63</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-70.25615</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>-18.05259</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-70.25391</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>837146</t>
+          <t>718025</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SAN JOSE DE NAZARET</t>
+          <t>43508 PROCER MANUEL CALDERON DE LA BARCA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-18.02703</t>
+          <t>775</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-70.24281</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>501</t>
+          <t>-18.0730569112003</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>-70.2595473938168</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1245,42 +1245,42 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>486836</t>
+          <t>668577</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>42253 GERARDO ARIAS COPAJA</t>
+          <t>456 EL CARMELO DE MARIA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-18.05123</t>
+          <t>423</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-70.25725</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>-18.08729</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>-70.27736</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>809233</t>
+          <t>668515</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SANTA CRUZ</t>
+          <t>450 ENRIQUE DELHORME</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-18.06338</t>
+          <t>213</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-70.25691</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1031</t>
+          <t>-18.0699</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>-70.2409</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>808455</t>
+          <t>623862</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>42255 SANTA TERESITA DEL NIÑO JESUS</t>
+          <t>SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-18.03938</t>
+          <t>149</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-70.24599</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>-18.05025</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>-70.24346</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>809214</t>
+          <t>486836</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>DR. JOSE ANTONIO ENCINAS FRANCO</t>
+          <t>42253 GERARDO ARIAS COPAJA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-18.06851</t>
+          <t>975</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-70.24763</t>
+          <t>49</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>-18.05123</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>-70.25725</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>486285</t>
+          <t>486544</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>419</t>
+          <t>42238 ENRIQUE PAILLARDELLE</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-18.05448</t>
+          <t>1799</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-70.2496</t>
+          <t>93</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>-18.047217</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-70.250942</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>486544</t>
+          <t>486539</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>42238 ENRIQUE PAILLARDELLE</t>
+          <t>42237 JORGE CHAVEZ</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-18.047217</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-70.250942</t>
+          <t>99</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1799</t>
+          <t>-18.04038</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>-70.25572</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>486539</t>
+          <t>486285</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>42237 JORGE CHAVEZ</t>
+          <t>419</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-18.04038</t>
+          <t>151</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-70.25572</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>-18.05448</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>-70.2496</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,37 +1679,37 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>808653</t>
+          <t>254025</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>LUIS ALBERTO SANCHEZ</t>
+          <t>SAN MIGUEL ARCANGEL</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-18.05841</t>
+          <t>41</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-70.25076</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1854</t>
+          <t>-18.04626</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>-70.25615</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">

--- a/ZonasEscolares/excels/TACNA-TACNA-CORONEL_GREGORIO_ALBARRACIN_LANCHIPA.xlsx
+++ b/ZonasEscolares/excels/TACNA-TACNA-CORONEL_GREGORIO_ALBARRACIN_LANCHIPA.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
